--- a/data/synthetic/defra_2026.xlsx
+++ b/data/synthetic/defra_2026.xlsx
@@ -11,7 +11,6 @@
     <sheet name="UK electricity" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Material use" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Water supply" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Freighting goods" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -430,121 +429,163 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GHG Conversion Factors 2026 — for testing only</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Scope</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Level 1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Level 2</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Level 3</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Level 4</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Column Text</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>UOM</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>kg CO2e</t>
+          <t>Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Index</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Emissions source:</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Fuels</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Factor set:</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Full set</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Scope:</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Scope 1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Version:</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Year:</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Fuels conversion factors 2026 — for testing only</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Guidance</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>● Synthetic guidance line — not real DEFRA text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Fuel</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>kg CO2e</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Gaseous fuels</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Natural gas</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>kwh</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="D13" t="n">
         <v>0.1821</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Liquid fuels</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Diesel (average biofuel blend)</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>litre</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="D14" t="n">
         <v>2.662</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
         <is>
           <t>Petrol (average biofuel blend)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>litre</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="D15" t="n">
         <v>2.349</v>
       </c>
     </row>
@@ -559,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -572,77 +613,127 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GHG Conversion Factors 2026 — for testing only</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Scope</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Level 1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Level 2</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Level 3</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Level 4</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Column Text</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>UOM</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>kg CO2e</t>
+          <t>UK electricity</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Index</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Emissions source:</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>UK electricity</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Factor set:</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Full set</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Scope:</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Scope 2</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>UK electricity</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Version:</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Year:</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>UK electricity conversion factors 2026 — for testing only</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Guidance</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>● Synthetic guidance line — not real DEFRA text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>kg CO2e</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Electricity generated</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Electricity: UK</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>kwh</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="D13" t="n">
         <v>0.2251</v>
       </c>
     </row>
@@ -657,7 +748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,166 +761,217 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GHG Conversion Factors 2026 — for testing only</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Scope</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Level 1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Level 2</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Level 3</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Level 4</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Column Text</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>UOM</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>kg CO2e</t>
+          <t>Material use</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Index</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Emissions source:</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Material use</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Factor set:</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Full set</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Scope:</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Scope 3</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Version:</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Year:</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Material use conversion factors 2026 — for testing only</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Guidance</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>● Synthetic guidance line — not real DEFRA text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Primary material production</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Closed-loop source</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>kg CO2e</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>kg CO2e</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Metal</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Aluminium</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Primary material production</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>tonne</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="D14" t="n">
         <v>14200</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr">
+      <c r="E14" t="n">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Plastic</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Average plastics</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Primary material production</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>tonne</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="D15" t="n">
         <v>3450</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr">
+      <c r="E15" t="n">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Paper</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Board</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Primary material production</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>tonne</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="D16" t="n">
         <v>900</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr">
+      <c r="E16" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Glass</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Glass</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Primary material production</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>tonne</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="D17" t="n">
         <v>861</v>
+      </c>
+      <c r="E17" t="n">
+        <v>805</v>
       </c>
     </row>
   </sheetData>
@@ -843,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -856,180 +998,124 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GHG Conversion Factors 2026 — for testing only</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Scope</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Level 1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Level 2</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Level 3</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Level 4</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Column Text</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>UOM</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>kg CO2e</t>
+          <t>Water supply</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Index</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Emissions source:</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Water supply</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Factor set:</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Full set</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Scope:</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Scope 3</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Version:</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Year:</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Water supply conversion factors 2026 — for testing only</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Guidance</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>● Synthetic guidance line — not real DEFRA text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>kg CO2e</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Water supply</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Water supply</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
         <is>
           <t>cubic metre</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="D13" t="n">
         <v>0.149</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Freighting goods — Government conversion factors (SYNTHETIC)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>GHG Conversion Factors 2026 — for testing only</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Scope</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Level 1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Level 2</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Level 3</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Level 4</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Column Text</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>UOM</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>kg CO2e</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Scope 3</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>HGV (all diesel)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Rigid (&gt;7.5t-17t)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>50% laden</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>tonne.km</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0.1085</v>
       </c>
     </row>
   </sheetData>

--- a/data/synthetic/defra_2026.xlsx
+++ b/data/synthetic/defra_2026.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -587,6 +587,22 @@
       </c>
       <c r="D15" t="n">
         <v>2.349</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Fuel oil (mineral)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>litre</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>3.205</v>
       </c>
     </row>
   </sheetData>

--- a/data/synthetic/defra_2026.xlsx
+++ b/data/synthetic/defra_2026.xlsx
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.205</v>
+        <v>3.4</v>
       </c>
     </row>
   </sheetData>
